--- a/需調整部分.xlsx
+++ b/需調整部分.xlsx
@@ -107,7 +107,8 @@
         <charset val="136"/>
         <scheme val="minor"/>
       </rPr>
-      <t>都要調整</t>
+      <t>都要調整
+戶外照不需要</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -175,7 +176,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -205,6 +206,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -512,7 +516,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" t="s">
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
     </row>
